--- a/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-200_p-20_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-200_p-20_nm_basis-False_nm_modifier-False.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,609 +448,324 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sub6ex1</t>
+          <t>sub1ex1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.50511682627013</v>
+        <v>79.53304094326076</v>
       </c>
       <c r="C2" t="n">
-        <v>81.10396134606167</v>
+        <v>79.08482266423955</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6036248681368306</v>
+        <v>0.6032482774307331</v>
       </c>
       <c r="E2" t="n">
-        <v>81.50511682627011</v>
+        <v>79.53304094326076</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sub6ex2</t>
+          <t>sub1ex2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>85.52089550947673</v>
+        <v>74.43654356871599</v>
       </c>
       <c r="C3" t="n">
-        <v>85.2552219403467</v>
+        <v>74.40014011482988</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4205841005779803</v>
+        <v>0.638910997658968</v>
       </c>
       <c r="E3" t="n">
-        <v>85.52089550947673</v>
+        <v>74.43654356871599</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sub6ex3</t>
+          <t>sub1ex3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84.60263497089075</v>
+        <v>73.14777809496623</v>
       </c>
       <c r="C4" t="n">
-        <v>84.08453204517282</v>
+        <v>73.10503160858431</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4386492223478854</v>
+        <v>0.6815509282052516</v>
       </c>
       <c r="E4" t="n">
-        <v>84.60263497089075</v>
+        <v>73.14777809496623</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sub7ex1</t>
+          <t>sub2ex1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.18111748371525</v>
+        <v>78.56356888900423</v>
       </c>
       <c r="C5" t="n">
-        <v>76.26906907438122</v>
+        <v>78.28851097789577</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6494703566034634</v>
+        <v>0.606023071706295</v>
       </c>
       <c r="E5" t="n">
-        <v>77.18111748371525</v>
+        <v>78.56356888900423</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sub7ex2</t>
+          <t>sub2ex2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>79.96366750577428</v>
+        <v>73.62243618024378</v>
       </c>
       <c r="C6" t="n">
-        <v>79.59823496722035</v>
+        <v>72.15870457284204</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5641001099410157</v>
+        <v>1.018484844298412</v>
       </c>
       <c r="E6" t="n">
-        <v>79.96366750577427</v>
+        <v>73.62243618024378</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sub7ex3</t>
+          <t>sub2ex3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>74.12001833925899</v>
+        <v>78.35206186904732</v>
       </c>
       <c r="C7" t="n">
-        <v>74.07583197314614</v>
+        <v>78.08455091276844</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6779895152896642</v>
+        <v>0.5201559399565061</v>
       </c>
       <c r="E7" t="n">
-        <v>74.12001833925899</v>
+        <v>78.35206186904732</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sub8ex1</t>
+          <t>sub3ex1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>87.25767523940519</v>
+        <v>71.78496353774686</v>
       </c>
       <c r="C8" t="n">
-        <v>87.21107130855016</v>
+        <v>71.72493561089365</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3228477412330297</v>
+        <v>0.7692762794593969</v>
       </c>
       <c r="E8" t="n">
-        <v>87.25767523940519</v>
+        <v>71.78496353774686</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sub8ex2</t>
+          <t>sub3ex2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89.11798544970112</v>
+        <v>82.8325504545887</v>
       </c>
       <c r="C9" t="n">
-        <v>89.06517337757407</v>
+        <v>81.11716477914732</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3080349416549628</v>
+        <v>0.5145072253110509</v>
       </c>
       <c r="E9" t="n">
-        <v>89.11798544970112</v>
+        <v>82.8325504545887</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sub8ex3</t>
+          <t>sub3ex3</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90.85649529840222</v>
+        <v>86.22695698059673</v>
       </c>
       <c r="C10" t="n">
-        <v>90.89800797343602</v>
+        <v>85.74248230199157</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2229967847194833</v>
+        <v>0.3592591313800464</v>
       </c>
       <c r="E10" t="n">
-        <v>90.85649529840222</v>
+        <v>86.22695698059673</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sub9ex1</t>
+          <t>sub4ex1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>88.23389475687506</v>
+        <v>75.44278064689141</v>
       </c>
       <c r="C11" t="n">
-        <v>87.9813480308777</v>
+        <v>75.20078089812426</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3388113363645971</v>
+        <v>0.7360034911582868</v>
       </c>
       <c r="E11" t="n">
-        <v>88.23389475687506</v>
+        <v>75.44278064689141</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sub9ex2</t>
+          <t>sub4ex2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>82.39076462599158</v>
+        <v>69.4545800569209</v>
       </c>
       <c r="C12" t="n">
-        <v>81.82814587108804</v>
+        <v>69.10403709188546</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5167054487547527</v>
+        <v>0.8000956413646539</v>
       </c>
       <c r="E12" t="n">
-        <v>82.39076462599158</v>
+        <v>69.4545800569209</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sub9ex3</t>
+          <t>sub4ex3</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>88.70241092050969</v>
+        <v>76.02115935258955</v>
       </c>
       <c r="C13" t="n">
-        <v>87.80093430635303</v>
+        <v>75.97888606362523</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3889663657794396</v>
+        <v>0.6399980586022138</v>
       </c>
       <c r="E13" t="n">
-        <v>88.70241092050969</v>
+        <v>76.02115935258955</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sub10ex1</t>
+          <t>sub5ex1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>71.41463161446033</v>
+        <v>75.75463455566225</v>
       </c>
       <c r="C14" t="n">
-        <v>70.43502249582042</v>
+        <v>74.95485649630257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8035944854840636</v>
+        <v>0.6100029307728012</v>
       </c>
       <c r="E14" t="n">
-        <v>71.41463161446033</v>
+        <v>75.75463455566225</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sub10ex2</t>
+          <t>sub5ex2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>82.50979679755015</v>
+        <v>76.61061081843269</v>
       </c>
       <c r="C15" t="n">
-        <v>82.56709887624231</v>
+        <v>76.27738551148728</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4552288515182833</v>
+        <v>0.6650489268824458</v>
       </c>
       <c r="E15" t="n">
-        <v>82.50979679755014</v>
+        <v>76.61061081843269</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sub10ex3</t>
+          <t>sub5ex3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>76.67514424865267</v>
+        <v>66.52471042137043</v>
       </c>
       <c r="C16" t="n">
-        <v>76.21291558707796</v>
+        <v>66.46503590078575</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6048521329959233</v>
+        <v>0.9098423908309391</v>
       </c>
       <c r="E16" t="n">
-        <v>76.67514424865267</v>
+        <v>66.52471042137043</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sub11ex1</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>81.86999887542279</v>
+        <v>75.88722509133585</v>
       </c>
       <c r="C17" t="n">
-        <v>81.67353266499505</v>
+        <v>75.4458217003602</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4955094040371478</v>
+        <v>0.6714938756678667</v>
       </c>
       <c r="E17" t="n">
-        <v>81.86999887542279</v>
+        <v>75.88722509133585</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sub11ex2</t>
+          <t>Std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>81.5365184819938</v>
+        <v>4.782165580015456</v>
       </c>
       <c r="C18" t="n">
-        <v>81.02301154909171</v>
+        <v>4.617674941694965</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5455199632405614</v>
+        <v>0.1565106814431074</v>
       </c>
       <c r="E18" t="n">
-        <v>81.5365184819938</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>sub11ex3</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>89.17421430981237</v>
-      </c>
-      <c r="C19" t="n">
-        <v>89.18584934301964</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.3309975256871743</v>
-      </c>
-      <c r="E19" t="n">
-        <v>89.17421430981237</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>sub12ex1</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>80.38919021790846</v>
-      </c>
-      <c r="C20" t="n">
-        <v>79.84855576817515</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.5330074199164907</v>
-      </c>
-      <c r="E20" t="n">
-        <v>80.38919021790846</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>sub12ex2</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>75.90835560861254</v>
-      </c>
-      <c r="C21" t="n">
-        <v>75.45669762851702</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.6454794478913148</v>
-      </c>
-      <c r="E21" t="n">
-        <v>75.90835560861254</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>sub12ex3</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>81.92138340297062</v>
-      </c>
-      <c r="C22" t="n">
-        <v>81.42121714591016</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.5035052052699029</v>
-      </c>
-      <c r="E22" t="n">
-        <v>81.92138340297062</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>sub13ex1</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>76.5947802316629</v>
-      </c>
-      <c r="C23" t="n">
-        <v>76.12841866298686</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.6508381227652232</v>
-      </c>
-      <c r="E23" t="n">
-        <v>76.5947802316629</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>sub13ex2</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>83.30487287952317</v>
-      </c>
-      <c r="C24" t="n">
-        <v>83.1147172113314</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.4428970620346567</v>
-      </c>
-      <c r="E24" t="n">
-        <v>83.30487287952317</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>sub13ex3</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>81.01125442261612</v>
-      </c>
-      <c r="C25" t="n">
-        <v>80.41117583905057</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.4740004910000911</v>
-      </c>
-      <c r="E25" t="n">
-        <v>81.0112544226161</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>sub14ex1</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>83.69198695490445</v>
-      </c>
-      <c r="C26" t="n">
-        <v>83.488463571415</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.4213083317813774</v>
-      </c>
-      <c r="E26" t="n">
-        <v>83.69198695490445</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>sub14ex2</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>75.43793631432797</v>
-      </c>
-      <c r="C27" t="n">
-        <v>75.16970910246742</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.6588367225291828</v>
-      </c>
-      <c r="E27" t="n">
-        <v>75.43793631432797</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>sub14ex3</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>81.74041297935102</v>
-      </c>
-      <c r="C28" t="n">
-        <v>81.61393918890995</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.5072755134897307</v>
-      </c>
-      <c r="E28" t="n">
-        <v>81.74041297935102</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>sub15ex1</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>88.62671822420609</v>
-      </c>
-      <c r="C29" t="n">
-        <v>88.60098247616483</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.36829773306672</v>
-      </c>
-      <c r="E29" t="n">
-        <v>88.62671822420609</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>sub15ex2</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>89.29307346949368</v>
-      </c>
-      <c r="C30" t="n">
-        <v>89.32142096253259</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.2997633178776596</v>
-      </c>
-      <c r="E30" t="n">
-        <v>89.29307346949368</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>sub15ex3</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>90.06574451336084</v>
-      </c>
-      <c r="C31" t="n">
-        <v>89.64476245367862</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.314340161307094</v>
-      </c>
-      <c r="E31" t="n">
-        <v>90.06574451336084</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>82.68728968243668</v>
-      </c>
-      <c r="C32" t="n">
-        <v>82.34963409138649</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.48360108944319</v>
-      </c>
-      <c r="E32" t="n">
-        <v>82.68728968243668</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Std</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>5.188158844705534</v>
-      </c>
-      <c r="C33" t="n">
-        <v>5.323220467110819</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.1369411673475088</v>
-      </c>
-      <c r="E33" t="n">
-        <v>5.188158844705535</v>
+        <v>4.782165580015456</v>
       </c>
     </row>
   </sheetData>
@@ -1096,16 +811,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82.68728968243668</v>
+        <v>75.88722509133585</v>
       </c>
       <c r="B2" t="n">
-        <v>82.34963409138649</v>
+        <v>75.4458217003602</v>
       </c>
       <c r="C2" t="n">
-        <v>0.48360108944319</v>
+        <v>0.6714938756678667</v>
       </c>
       <c r="D2" t="n">
-        <v>82.68728968243668</v>
+        <v>75.88722509133585</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1115,16 +830,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5.188158844705534</v>
+        <v>4.782165580015456</v>
       </c>
       <c r="B3" t="n">
-        <v>5.323220467110819</v>
+        <v>4.617674941694965</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1369411673475088</v>
+        <v>0.1565106814431074</v>
       </c>
       <c r="D3" t="n">
-        <v>5.188158844705535</v>
+        <v>4.782165580015456</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1190,28 +905,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82.68728968243668</v>
+        <v>75.88722509133585</v>
       </c>
       <c r="B2" t="n">
-        <v>5.188158844705534</v>
+        <v>4.782165580015456</v>
       </c>
       <c r="C2" t="n">
-        <v>82.34963409138649</v>
+        <v>75.4458217003602</v>
       </c>
       <c r="D2" t="n">
-        <v>5.323220467110819</v>
+        <v>4.617674941694965</v>
       </c>
       <c r="E2" t="n">
-        <v>82.68728968243668</v>
+        <v>75.88722509133585</v>
       </c>
       <c r="F2" t="n">
-        <v>5.188158844705535</v>
+        <v>4.782165580015456</v>
       </c>
       <c r="G2" t="n">
-        <v>0.48360108944319</v>
+        <v>0.6714938756678667</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1369411673475088</v>
+        <v>0.1565106814431074</v>
       </c>
     </row>
   </sheetData>
